--- a/artfynd/A 33928-2022 artfynd.xlsx
+++ b/artfynd/A 33928-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33928-2022 artfynd.xlsx
+++ b/artfynd/A 33928-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17134872</v>
+        <v>17134873</v>
       </c>
       <c r="B2" t="n">
-        <v>96246</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223578</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>3</t>
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515674.9484704257</v>
+        <v>515675</v>
       </c>
       <c r="R2" t="n">
-        <v>6949785.569461385</v>
+        <v>6949786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,19 +752,9 @@
           <t>1994-07-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1994-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -805,12 +794,7 @@
         <v>17134874</v>
       </c>
       <c r="B3" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515674.9484704257</v>
+        <v>515675</v>
       </c>
       <c r="R3" t="n">
-        <v>6949785.569461385</v>
+        <v>6949786</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,19 +868,9 @@
           <t>1994-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1994-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -933,15 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17134873</v>
+        <v>17134876</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,31 +918,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>222467</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Gräsull</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Eriophorum latifolium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>Hoppe</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515674.9484704257</v>
+        <v>515675</v>
       </c>
       <c r="R4" t="n">
-        <v>6949785.569461385</v>
+        <v>6949786</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,19 +984,9 @@
           <t>1994-07-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1994-07-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1064,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17134876</v>
+        <v>17134872</v>
       </c>
       <c r="B5" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,31 +1034,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222467</v>
+        <v>223578</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräsull</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eriophorum latifolium</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Hoppe</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1113,10 +1063,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515674.9484704257</v>
+        <v>515675</v>
       </c>
       <c r="R5" t="n">
-        <v>6949785.569461385</v>
+        <v>6949786</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1146,19 +1096,9 @@
           <t>1994-07-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1994-07-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1192,6 +1132,118 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>17134846</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Löningsberg /800 m SSV/, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6949780</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1994-07-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1994-07-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Trakt: 18F0e13, taxyta: N1000. Tall planterad.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Hygge</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström, Eva Jonsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33928-2022 artfynd.xlsx
+++ b/artfynd/A 33928-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17134873</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17134874</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17134876</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1132,6 +1152,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17134872</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,8 +1269,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17134846</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>